--- a/Result/checksun_type/租賃業.xlsx
+++ b/Result/checksun_type/租賃業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>103.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>102.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>107.13</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>107.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>869583680.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>875265539.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>875265539.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>806927669.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>688847468.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>688847468.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>56843675.01200628</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>869583680</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>869583680.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>102.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>102.65</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>107.37</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>107.37</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>619351701.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>842957586.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>842957586.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>764135866.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>680345523.52</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>680345523.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>59520462.50443006</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>619351701</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>619351701.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>101.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>102.7</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>107.59</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>107.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1517534993.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>933815396.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>933815396.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>758867372.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>678605221.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>678605221.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>88029283.01130593</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1517534993</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1517534993.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>101.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>107.83</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>107.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>797540438.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>779805058.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>779805058.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>635921294.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>655427263.24</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>655427263.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>29378342.34215343</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>797540438</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>797540438.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>100.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>108.1</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>108.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>572316887.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>725056626.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>725056626.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>596629497.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>645369101.8</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>645369101.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>21684331.48114443</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>572316887</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>572316887.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>100.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>102.95</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>108.4</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>108.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>708043915.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>738589798.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>738589798.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>603958549.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>640637273.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>640637273.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>34049541.73394787</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>708043915</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>708043915.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.6</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>103.1</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>108.74</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>108.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1073640748.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>685314147.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>685314147</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>590241006.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>636004966.32</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>636004966.3200001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>35955891.17602599</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1073640748</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1073640748.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>103.35</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>109.06</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>109.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>747483306.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>583919349.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>583919349</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>517939589.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>624727235.74</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>624727235.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1775980.698720574</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>747483306</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>747483306.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>102.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>103.62</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>109.36</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>103.62</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>109.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>523798275.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>492037530.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>492037530.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>534026594.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>616710120.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>616710120.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-20669786.70911843</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>523798275</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>523798275.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>103.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>103.85</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>109.63</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>109.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>639982747.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>468202369.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>468202369</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>548528419.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>621932648.88</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>621932648.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-22956478.16293263</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>639982747</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>639982747.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>103.5</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>109.91</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>109.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>441665659.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>469327301.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>469327301.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>540333121.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>624789224.54</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>624789224.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-37851642.3054195</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>441665659</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>441665659.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>2834</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6029,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6213,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>21.36</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6264,16 @@
           <t>116282419.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>147052327.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>147052327.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>138102467.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>155068162.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>155068162.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6290,10 @@
           <t>1204165.073090315</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>116282419</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>116282419.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6643,11 @@
           <t>21.03</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>21.39</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>21.98</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>21.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6694,16 @@
           <t>94530656.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>154156015.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>154156015.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>136238579.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>156428624.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>156428624.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6720,10 @@
           <t>3769771.452193916</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>94530656</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>94530656.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6889,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7073,11 @@
           <t>21.04</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21.99</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7124,16 @@
           <t>253863086.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>171154981.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>171154981</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>133468139.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>156046599.04</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>156046599.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7150,10 @@
           <t>9630834.76333502</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>253863086</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>253863086.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7503,11 @@
           <t>21.11</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7554,16 @@
           <t>153541023.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>149322704.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>149322704.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>117000702.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>152229876.58</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>152229876.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7580,10 @@
           <t>588492.1805603057</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>153541023</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>153541023.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7933,11 @@
           <t>21.21</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>22.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7984,16 @@
           <t>117044452.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>142327035.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>142327035.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>113627876.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>150846262.58</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>150846262.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8010,10 @@
           <t>-1601365.194137841</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>117044452</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>117044452.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8363,11 @@
           <t>21.28</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>22.03</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>22.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8414,16 @@
           <t>151800860.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>129152608.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>129152608.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>108888887.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>149915951.98</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>149915951.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8440,10 @@
           <t>-762194.3653445691</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>151800860</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>151800860.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8793,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>21.64</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>22.04</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>22.04</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8844,16 @@
           <t>179525484.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>118321143.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>118321143.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>107889966.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>148811831.48</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>148811831.48</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8870,10 @@
           <t>-3260058.525449008</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>179525484</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>179525484.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9223,11 @@
           <t>21.48</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9274,16 @@
           <t>144701702.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>95781297.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>95781297.59999999</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>98681638.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>146653963.74</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>146653963.74</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9300,10 @@
           <t>-9682500.663975045</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>144701702</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>144701702.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9469,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9653,11 @@
           <t>21.52</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9704,16 @@
           <t>118562679.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>84678701.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>84678701.40000001</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>93476777.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>145151087.98</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>145151087.98</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9730,10 @@
           <t>-14780494.90958455</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>118562679</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>118562679.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10083,11 @@
           <t>21.56</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10134,16 @@
           <t>51172318.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>84928718.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>84928718</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>98125994.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>144492728.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>144492728.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10160,10 @@
           <t>-18734859.40654151</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>51172318</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>51172318.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10329,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10513,11 @@
           <t>21.59</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>21.82</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10564,16 @@
           <t>97643536.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>88625166.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>88625166.59999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>110514630.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>145223381.52</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>145223381.52</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>-16494453.60196072</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>97643536</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>97643536.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>13.65</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13.32</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.32</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>4314746.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4978301.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4978301.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4517684.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>4713760.62</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>4713760.62</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>27641.80035279691</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>4314746</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>4314746.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>13.53</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>2757942.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4746919.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4746919.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4730599.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>4734328.96</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>4734328.96</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>64481.15028462093</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2757942</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2757942.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>8651275.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>5201761.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>5201761.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>4754039.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>4800272.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>4800272.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>281606.3233913472</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>8651275</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>8651275.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.3</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>3707868.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4136832.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4136832.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4711853.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>4713576.58</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>4713576.58</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>-49700.76229159161</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3707868</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3707868.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>5459676.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4186896.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4186896</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>4402878.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>4751543.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>4751543.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>8429.178243194707</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5459676</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5459676.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>3157835.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4057067.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4057067.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>4239221.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>5062110.22</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>5062110.22</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>-96522.80593008175</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>3157835</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>3157835.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>5032153.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4714280.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4714280.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>4265300.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>5387852.96</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>5387852.96</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>3618.852605597116</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5032153</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5032153.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>13.47</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>3326632.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>4306316.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>4306316.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>4483139.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>5335377.72</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>5335377.72</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>-54270.66565077566</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3326632</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3326632.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.21</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.28</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>3958184.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5286874.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>5286874.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4828292.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>5326099.52</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>5326099.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>47702.65347050503</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3958184</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3958184.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.28</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>4810532.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>4618861.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>4618861.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>5030972.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>5401520.16</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>5401520.16</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>124008.8717341041</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>4810532</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>4810532.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>13.34</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>13.27</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>6443900.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>4421375.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>4421375.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>4897374.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>5403235.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>5403235.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>137265.8666915996</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6443900</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6443900.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
